--- a/spreadsheet_codegen/examples/abs_fpi/ABS_FPI_load_cases.xlsx
+++ b/spreadsheet_codegen/examples/abs_fpi/ABS_FPI_load_cases.xlsx
@@ -1053,7 +1053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B32"/>
+  <dimension ref="A1:A32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1100,7 +1100,7 @@
     <row r="7">
       <c r="A7" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">          excel-codegen render -c &lt;配置&gt;.yaml -x ABS_FPI_load_cases.xlsx --write-excel</t>
+          <t xml:space="preserve">          spreadsheet-codegen render -c &lt;配置&gt;.yaml -x ABS_FPI_load_cases.xlsx --write-excel</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
     <row r="10">
       <c r="A10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">      想确认表里的代码是不是已经过期：excel-codegen check -c &lt;配置&gt;.yaml</t>
+          <t xml:space="preserve">      想确认表里的代码是不是已经过期：spreadsheet-codegen check -c &lt;配置&gt;.yaml</t>
         </is>
       </c>
     </row>
@@ -2743,7 +2743,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:D94"/>
+  <dimension ref="A1:D92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="2" max="2"/>
@@ -4042,8 +4042,6 @@
         <v/>
       </c>
     </row>
-    <row r="93"/>
-    <row r="94"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4055,7 +4053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:X6"/>
+  <dimension ref="A1:X4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -4083,6 +4081,7 @@
     <col width="160" customWidth="1" min="24" max="24"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
@@ -4380,8 +4379,6 @@
         <v/>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4393,7 +4390,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E127"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="160" customWidth="1" min="2" max="2"/>
@@ -6656,8 +6653,6 @@
         <v/>
       </c>
     </row>
-    <row r="126"/>
-    <row r="127"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6669,7 +6664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AE7"/>
+  <dimension ref="A1:AE5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="2" max="2"/>
@@ -6704,6 +6699,7 @@
     <col width="160" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="A2" s="19" t="inlineStr">
         <is>
@@ -7212,8 +7208,6 @@
         <v/>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10270,7 +10264,7 @@
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t>## excel-codegen-meta</t>
+          <t>## spreadsheet-codegen-meta</t>
         </is>
       </c>
     </row>
